--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486881_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486881_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.940200000000001</v>
+        <v>7.9272</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8047</v>
+        <v>6.1771</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1355</v>
+        <v>1.7501</v>
       </c>
       <c r="G2" t="n">
         <v>5.686</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6997</v>
+        <v>0.6868</v>
       </c>
       <c r="T2" t="n">
-        <v>0.736</v>
+        <v>0.1084</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9638</v>
+        <v>0.5784</v>
       </c>
       <c r="V2" t="n">
         <v>0.9384</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4952</v>
+        <v>5.3919</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6805</v>
+        <v>2.7206</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8147</v>
+        <v>2.6713</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4088</v>
+        <v>4.0892</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.009599999999999999</v>
+        <v>3.2735</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4185</v>
+        <v>0.8157</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0526</v>
+        <v>3.9016</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2633</v>
+        <v>3.2966</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7893</v>
+        <v>0.605</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3562</v>
+        <v>0.1876</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2729</v>
+        <v>-0.0231</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6291</v>
+        <v>0.2107</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2301</v>
+        <v>-0.2867</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2357</v>
+        <v>-0.3062</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9944</v>
+        <v>0.0195</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4189</v>
+        <v>1.1786</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4189</v>
+        <v>1.1786</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7363</v>
+        <v>5.1388</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3022</v>
+        <v>1.7391</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4341</v>
+        <v>3.3997</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0892</v>
+        <v>1.4088</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2735</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8157</v>
+        <v>1.4185</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9016</v>
+        <v>1.0526</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2966</v>
+        <v>0.2633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.605</v>
+        <v>0.7893</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1876</v>
+        <v>0.3562</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0231</v>
+        <v>-0.2729</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2107</v>
+        <v>0.6291</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
         <v>2.4641</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9422</v>
+        <v>0.8737</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7246</v>
+        <v>0.2943</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2176</v>
+        <v>0.5794</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3333</v>
+        <v>3.4511</v>
       </c>
       <c r="E5" t="n">
-        <v>2.667</v>
+        <v>1.7256</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6663</v>
+        <v>1.7256</v>
       </c>
       <c r="G5" t="n">
         <v>1.815</v>
@@ -844,13 +844,13 @@
         <v>2.6694</v>
       </c>
       <c r="S5" t="n">
-        <v>0.547</v>
+        <v>-0.3352</v>
       </c>
       <c r="T5" t="n">
-        <v>1.104</v>
+        <v>0.1626</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.4977</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6982</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2283</v>
+        <v>2.1819</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2951</v>
+        <v>1.9227</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0668</v>
+        <v>0.2592</v>
       </c>
       <c r="G6" t="n">
         <v>4.0376</v>
@@ -922,13 +922,13 @@
         <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.604</v>
+        <v>0.3497</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6587</v>
+        <v>-0.0311</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0547</v>
+        <v>0.3808</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1786</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7085</v>
+        <v>1.3344</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.145</v>
+        <v>-0.7266</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8535</v>
+        <v>2.061</v>
       </c>
       <c r="G7" t="n">
         <v>0.5856</v>
@@ -1000,13 +1000,13 @@
         <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6985</v>
+        <v>-0.0726</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4611</v>
+        <v>-0.0427</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2374</v>
+        <v>-0.0299</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CLIMENT FIGUERES</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.2345</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0264</v>
+        <v>0.2011</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0552</v>
+        <v>0.0334</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0157</v>
+        <v>0.6775</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1947</v>
+        <v>0.8304</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1789</v>
+        <v>-0.1529</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0395</v>
+        <v>1.2976</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.5217</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>-0.2241</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0552</v>
+        <v>-0.6201</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1947</v>
+        <v>-0.6913</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1395</v>
+        <v>0.0713</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0659</v>
+        <v>-0.4697</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0659</v>
+        <v>-0.0698</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.3999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>J. CLIMENT FIGUERES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1284</v>
+        <v>0.023</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9734</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.845</v>
+        <v>-0.0552</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2446</v>
+        <v>-0.0157</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4156</v>
+        <v>-0.1947</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6602</v>
+        <v>0.1789</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6961</v>
+        <v>0.0395</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5256</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1706</v>
+        <v>0.0395</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4515</v>
+        <v>-0.0552</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9412</v>
+        <v>-0.1947</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4897</v>
+        <v>0.1395</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4374</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1758</v>
+        <v>0.0387</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1704</v>
+        <v>0.0387</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3462</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4367</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3219</v>
+        <v>0.7018</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1148</v>
+        <v>-0.7683</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6775</v>
+        <v>2.2021</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8304</v>
+        <v>-0.6233</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1529</v>
+        <v>2.8255</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2976</v>
+        <v>3.1273</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5217</v>
+        <v>0.2336</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2241</v>
+        <v>2.8937</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6201</v>
+        <v>-0.9251</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6913</v>
+        <v>-0.8569</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0713</v>
+        <v>-0.0682</v>
       </c>
       <c r="P10" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6427</v>
+        <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.141</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5928</v>
+        <v>-0.3721</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5481</v>
+        <v>-0.334</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5893</v>
+        <v>-1.7679</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5893</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6332</v>
+        <v>-0.2469</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2834</v>
+        <v>-0.9734</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9166</v>
+        <v>0.7264</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2021</v>
+        <v>1.2446</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6233</v>
+        <v>-0.4156</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8255</v>
+        <v>1.6602</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1273</v>
+        <v>1.6961</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2336</v>
+        <v>0.5256</v>
       </c>
       <c r="L11" t="n">
-        <v>2.8937</v>
+        <v>1.1706</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9251</v>
+        <v>-0.4515</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8569</v>
+        <v>-0.9412</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0682</v>
+        <v>0.4897</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2053</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2588</v>
+        <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2727</v>
+        <v>-0.2944</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7905</v>
+        <v>0.1704</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4823</v>
+        <v>-0.4648</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7679</v>
+        <v>0.2402</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>J. BARBER TERRADES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.487</v>
+        <v>-2.7387</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1041</v>
+        <v>-0.5316</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6172</v>
+        <v>-2.2071</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0934</v>
+        <v>1.1877</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.083</v>
+        <v>-0.1752</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0104</v>
+        <v>1.3629</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1944</v>
+        <v>1.2429</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3917</v>
+        <v>0.0195</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1973</v>
+        <v>1.2234</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.899</v>
+        <v>-0.0552</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6913</v>
+        <v>-0.1947</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2077</v>
+        <v>0.1395</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.4374</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0438</v>
+        <v>0.0387</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1704</v>
+        <v>0.0387</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1265</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.117</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BARBER TERRADES</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8433</v>
+        <v>-2.7991</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6362</v>
+        <v>-3.2087</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2071</v>
+        <v>0.4097</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1877</v>
+        <v>-1.0934</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1752</v>
+        <v>-1.083</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3629</v>
+        <v>-0.0104</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2429</v>
+        <v>-0.1944</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0195</v>
+        <v>-0.3917</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2234</v>
+        <v>0.1973</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0552</v>
+        <v>-0.899</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1947</v>
+        <v>-0.6913</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1395</v>
+        <v>-0.2077</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8481</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0659</v>
+        <v>-0.2683</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0659</v>
+        <v>0.0658</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0.334</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.117</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.83160000000001</v>
+        <v>19.8315</v>
       </c>
       <c r="E14" t="n">
-        <v>9.825899999999999</v>
+        <v>9.825900000000003</v>
       </c>
       <c r="F14" t="n">
         <v>10.0058</v>
@@ -1546,19 +1546,19 @@
         <v>20.534</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4453999999999998</v>
+        <v>-0.4454</v>
       </c>
       <c r="T14" t="n">
-        <v>0.05700000000000034</v>
+        <v>0.05699999999999995</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5022000000000003</v>
+        <v>-0.5022</v>
       </c>
       <c r="V14" t="n">
         <v>-2.5749</v>
       </c>
       <c r="W14" t="n">
-        <v>4.7369</v>
+        <v>4.736899999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-7.312000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6824</v>
+        <v>4.3856</v>
       </c>
       <c r="E15" t="n">
-        <v>6.7612</v>
+        <v>4.1461</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9212</v>
+        <v>0.2395</v>
       </c>
       <c r="G15" t="n">
         <v>0.6091</v>
@@ -1624,13 +1624,13 @@
         <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>4.6441</v>
+        <v>1.3472</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7694</v>
+        <v>1.1543</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8747</v>
+        <v>0.1929</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2402</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3133</v>
+        <v>1.1485</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8919</v>
+        <v>1.5195</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5785</v>
+        <v>-0.371</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3906</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9388</v>
+        <v>-0.1037</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5192</v>
+        <v>0.1084</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4196</v>
+        <v>-0.2121</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6447000000000001</v>
+        <v>0.1608</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3402</v>
+        <v>-0.7125</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6955</v>
+        <v>0.8733</v>
       </c>
       <c r="G17" t="n">
         <v>-2.0825</v>
@@ -1780,13 +1780,13 @@
         <v>3.4908</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7141</v>
+        <v>-0.9086</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0462</v>
+        <v>-0.4186</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.49</v>
       </c>
       <c r="V17" t="n">
         <v>2.9466</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9978</v>
+        <v>-1.2685</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2467</v>
+        <v>-0.0327</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2446</v>
+        <v>-1.2358</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.872</v>
+        <v>-0.2804</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.175</v>
+        <v>-1.4567</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.697</v>
+        <v>1.1763</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6633</v>
+        <v>2.5207</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9923</v>
+        <v>0.6263</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6709000000000001</v>
+        <v>1.8944</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.5352</v>
+        <v>-2.8011</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1673</v>
+        <v>-2.083</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3679</v>
+        <v>-0.7181</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.4641</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.3122</v>
+        <v>-2.2588</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1596</v>
+        <v>-0.2674</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5384</v>
+        <v>-0.2946</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6212</v>
+        <v>0.0272</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>-0.7207</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0096</v>
+        <v>-1.5023</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5753</v>
+        <v>-1.1569</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4343</v>
+        <v>-0.3454</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4382</v>
@@ -1936,13 +1936,13 @@
         <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4831</v>
+        <v>0.0242</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5928</v>
+        <v>-0.1744</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1097</v>
+        <v>0.1986</v>
       </c>
       <c r="V19" t="n">
         <v>1.5277</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1332</v>
+        <v>-1.6238</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6603</v>
+        <v>0.8283</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4729</v>
+        <v>-2.4521</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2804</v>
+        <v>-0.872</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4567</v>
+        <v>-0.175</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1763</v>
+        <v>-0.697</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5207</v>
+        <v>2.6633</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6263</v>
+        <v>1.9923</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8944</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8011</v>
+        <v>-3.5352</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.083</v>
+        <v>-2.1673</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7181</v>
+        <v>-1.3679</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2588</v>
+        <v>-4.3122</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1321</v>
+        <v>0.5337</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9222</v>
+        <v>0.12</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2099</v>
+        <v>0.4137</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7207</v>
+        <v>1.1786</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7207</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9306</v>
+        <v>-2.3326</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5583</v>
+        <v>0.0693</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3723</v>
+        <v>-2.4019</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2282</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5854</v>
+        <v>0.0126</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3875</v>
+        <v>0.2401</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1979</v>
+        <v>-0.2275</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9384</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3665</v>
+        <v>-4.0684</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7202</v>
+        <v>-4.511</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3537</v>
+        <v>0.4426</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7516</v>
@@ -2170,13 +2170,13 @@
         <v>2.2588</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8202</v>
+        <v>-0.5221</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7905</v>
+        <v>-0.5813</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0298</v>
+        <v>0.0592</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7607</v>
+        <v>-5.942</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4019</v>
+        <v>-2.8203</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3588</v>
+        <v>-3.1216</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7521</v>
@@ -2248,13 +2248,13 @@
         <v>0.4107</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8128</v>
+        <v>0.6315</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9336</v>
+        <v>0.5152</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1208</v>
+        <v>0.1163</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.984299999999999</v>
+        <v>-8.789</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.6494</v>
+        <v>-7.3356</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3348</v>
+        <v>-1.4534</v>
       </c>
       <c r="G24" t="n">
         <v>-6.6387</v>
@@ -2326,13 +2326,13 @@
         <v>2.4641</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4975</v>
+        <v>-0.3022</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4806</v>
+        <v>-0.1668</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0168</v>
+        <v>-0.1354</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>4.8214</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.107399999999999</v>
+        <v>-2.1074</v>
       </c>
       <c r="M25" t="n">
         <v>-24.5393</v>
@@ -2395,7 +2395,7 @@
         <v>-8.5754</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.026800000000001</v>
+        <v>-1.0268</v>
       </c>
       <c r="Q25" t="n">
         <v>-20.5342</v>
@@ -2404,19 +2404,19 @@
         <v>19.5075</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4452999999999994</v>
+        <v>0.4451999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5023999999999998</v>
+        <v>0.5023</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.05699999999999988</v>
+        <v>-0.05709999999999991</v>
       </c>
       <c r="V25" t="n">
         <v>2.575</v>
       </c>
       <c r="W25" t="n">
-        <v>7.312000000000001</v>
+        <v>7.311999999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-4.7369</v>
